--- a/datos_Grup B.xlsx
+++ b/datos_Grup B.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U319"/>
+  <dimension ref="A1:S319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,16 +525,6 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Increment_x</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Increment_y</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
           <t>Increment</t>
         </is>
       </c>
@@ -604,7 +594,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>1830.92</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>21218</v>
@@ -615,14 +605,6 @@
       <c r="S2" t="n">
         <v>0.035</v>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -689,7 +671,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2156.38</v>
+        <v>2083.46</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>38648</v>
@@ -700,14 +682,6 @@
       <c r="S3" t="n">
         <v>0.035</v>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -774,7 +748,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1667.9</v>
+        <v>1611.5</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>18486</v>
@@ -785,14 +759,6 @@
       <c r="S4" t="n">
         <v>0.035</v>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -859,7 +825,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2187.44</v>
+        <v>2113.47</v>
       </c>
       <c r="Q5" s="2" t="n">
         <v>26020</v>
@@ -870,14 +836,6 @@
       <c r="S5" t="n">
         <v>0.035</v>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -940,7 +898,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1958.2</v>
+        <v>1891.98</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>20578</v>
@@ -951,14 +909,6 @@
       <c r="S6" t="n">
         <v>0.035</v>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1025,7 +975,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1581.13</v>
+        <v>1527.66</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>30543</v>
@@ -1036,14 +986,6 @@
       <c r="S7" t="n">
         <v>0.035</v>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1110,7 +1052,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1784.66</v>
+        <v>1724.31</v>
       </c>
       <c r="Q8" s="2" t="n">
         <v>19610</v>
@@ -1121,14 +1063,6 @@
       <c r="S8" t="n">
         <v>0.035</v>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U8" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1195,7 +1129,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1791.09</v>
+        <v>1730.52</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>29711</v>
@@ -1206,14 +1140,6 @@
       <c r="S9" t="n">
         <v>0.035</v>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U9" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1280,7 +1206,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1384.02</v>
+        <v>1337.22</v>
       </c>
       <c r="Q10" s="2" t="n">
         <v>28559</v>
@@ -1291,14 +1217,6 @@
       <c r="S10" t="n">
         <v>0.035</v>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U10" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1365,7 +1283,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1265.11</v>
+        <v>1222.33</v>
       </c>
       <c r="Q11" s="2" t="n">
         <v>29060</v>
@@ -1376,14 +1294,6 @@
       <c r="S11" t="n">
         <v>0.035</v>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U11" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1450,7 +1360,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1512.57</v>
+        <v>1461.42</v>
       </c>
       <c r="Q12" s="2" t="n">
         <v>33461</v>
@@ -1461,14 +1371,6 @@
       <c r="S12" t="n">
         <v>0.035</v>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U12" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1535,7 +1437,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1788.95</v>
+        <v>1728.45</v>
       </c>
       <c r="Q13" s="2" t="n">
         <v>30763</v>
@@ -1546,14 +1448,6 @@
       <c r="S13" t="n">
         <v>0.035</v>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U13" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1620,7 +1514,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1559.7</v>
+        <v>1506.96</v>
       </c>
       <c r="Q14" s="2" t="n">
         <v>26575</v>
@@ -1631,14 +1525,6 @@
       <c r="S14" t="n">
         <v>0.035</v>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U14" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1705,7 +1591,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1567.2</v>
+        <v>1514.2</v>
       </c>
       <c r="Q15" s="2" t="n">
         <v>21091</v>
@@ -1716,14 +1602,6 @@
       <c r="S15" t="n">
         <v>0.035</v>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U15" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1790,7 +1668,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2228.15</v>
+        <v>2152.8</v>
       </c>
       <c r="Q16" s="2" t="n">
         <v>37486</v>
@@ -1801,14 +1679,6 @@
       <c r="S16" t="n">
         <v>0.035</v>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U16" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1875,7 +1745,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2048.18</v>
+        <v>1978.92</v>
       </c>
       <c r="Q17" s="2" t="n">
         <v>29723</v>
@@ -1886,14 +1756,6 @@
       <c r="S17" t="n">
         <v>0.035</v>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U17" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1960,7 +1822,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2133.88</v>
+        <v>2061.72</v>
       </c>
       <c r="Q18" s="2" t="n">
         <v>34086</v>
@@ -1971,14 +1833,6 @@
       <c r="S18" t="n">
         <v>0.035</v>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U18" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2045,7 +1899,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1806.09</v>
+        <v>1745.01</v>
       </c>
       <c r="Q19" s="2" t="n">
         <v>19960</v>
@@ -2056,14 +1910,6 @@
       <c r="S19" t="n">
         <v>0.035</v>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U19" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2130,7 +1976,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1333.67</v>
+        <v>1288.57</v>
       </c>
       <c r="Q20" s="2" t="n">
         <v>33797</v>
@@ -2141,14 +1987,6 @@
       <c r="S20" t="n">
         <v>0.035</v>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U20" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2215,7 +2053,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1295.11</v>
+        <v>1251.31</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>29142</v>
@@ -2226,14 +2064,6 @@
       <c r="S21" t="n">
         <v>0.035</v>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U21" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2300,23 +2130,15 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2027.83</v>
+        <v>1959.26</v>
       </c>
       <c r="Q22" s="2" t="n">
         <v>25625</v>
       </c>
       <c r="R22" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S22" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U22" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -2385,7 +2207,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1269.4</v>
+        <v>1226.47</v>
       </c>
       <c r="Q23" s="2" t="n">
         <v>21799</v>
@@ -2396,14 +2218,6 @@
       <c r="S23" t="n">
         <v>0.035</v>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U23" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2470,7 +2284,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2185.3</v>
+        <v>2111.4</v>
       </c>
       <c r="Q24" s="2" t="n">
         <v>24851</v>
@@ -2481,14 +2295,6 @@
       <c r="S24" t="n">
         <v>0.035</v>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U24" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2555,7 +2361,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1632.55</v>
+        <v>1577.34</v>
       </c>
       <c r="Q25" s="2" t="n">
         <v>27367</v>
@@ -2566,14 +2372,6 @@
       <c r="S25" t="n">
         <v>0.035</v>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U25" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2640,7 +2438,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1788.95</v>
+        <v>1728.45</v>
       </c>
       <c r="Q26" s="2" t="n">
         <v>29289</v>
@@ -2651,14 +2449,6 @@
       <c r="S26" t="n">
         <v>0.035</v>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U26" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2725,7 +2515,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1559.7</v>
+        <v>1506.96</v>
       </c>
       <c r="Q27" s="2" t="n">
         <v>27884</v>
@@ -2736,14 +2526,6 @@
       <c r="S27" t="n">
         <v>0.035</v>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U27" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2810,23 +2592,15 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1429.01</v>
+        <v>1380.69</v>
       </c>
       <c r="Q28" s="2" t="n">
         <v>33659</v>
       </c>
       <c r="R28" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S28" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U28" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -2895,7 +2669,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2397.4</v>
+        <v>2316.33</v>
       </c>
       <c r="Q29" s="2" t="n">
         <v>21888</v>
@@ -2906,14 +2680,6 @@
       <c r="S29" t="n">
         <v>0.035</v>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U29" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2980,7 +2746,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1540.42</v>
+        <v>1488.33</v>
       </c>
       <c r="Q30" s="2" t="n">
         <v>35587</v>
@@ -2991,14 +2757,6 @@
       <c r="S30" t="n">
         <v>0.035</v>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U30" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3065,7 +2823,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1851.08</v>
+        <v>1788.48</v>
       </c>
       <c r="Q31" s="2" t="n">
         <v>21825</v>
@@ -3076,14 +2834,6 @@
       <c r="S31" t="n">
         <v>0.035</v>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U31" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3150,7 +2900,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1543.64</v>
+        <v>1491.44</v>
       </c>
       <c r="Q32" s="2" t="n">
         <v>21115</v>
@@ -3161,14 +2911,6 @@
       <c r="S32" t="n">
         <v>0.035</v>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U32" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3235,7 +2977,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1540.42</v>
+        <v>1488.33</v>
       </c>
       <c r="Q33" s="2" t="n">
         <v>22384</v>
@@ -3246,14 +2988,6 @@
       <c r="S33" t="n">
         <v>0.035</v>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U33" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3320,7 +3054,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2251.71</v>
+        <v>2175.57</v>
       </c>
       <c r="Q34" s="2" t="n">
         <v>29596</v>
@@ -3331,14 +3065,6 @@
       <c r="S34" t="n">
         <v>0.035</v>
       </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U34" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3405,7 +3131,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1604.7</v>
+        <v>1550.43</v>
       </c>
       <c r="Q35" s="2" t="n">
         <v>25510</v>
@@ -3416,14 +3142,6 @@
       <c r="S35" t="n">
         <v>0.035</v>
       </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U35" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3490,7 +3208,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1577.91</v>
+        <v>1524.55</v>
       </c>
       <c r="Q36" s="2" t="n">
         <v>22718</v>
@@ -3501,14 +3219,6 @@
       <c r="S36" t="n">
         <v>0.035</v>
       </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U36" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3575,7 +3285,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2203.52</v>
+        <v>2129</v>
       </c>
       <c r="Q37" s="2" t="n">
         <v>25893</v>
@@ -3586,14 +3296,6 @@
       <c r="S37" t="n">
         <v>0.035</v>
       </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U37" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3660,7 +3362,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1599.34</v>
+        <v>1545.26</v>
       </c>
       <c r="Q38" s="2" t="n">
         <v>31778</v>
@@ -3671,14 +3373,6 @@
       <c r="S38" t="n">
         <v>0.035</v>
       </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U38" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3745,7 +3439,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1610.05</v>
+        <v>1555.6</v>
       </c>
       <c r="Q39" s="2" t="n">
         <v>33312</v>
@@ -3756,14 +3450,6 @@
       <c r="S39" t="n">
         <v>0.035</v>
       </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U39" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3826,7 +3512,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1971.05</v>
+        <v>1904.4</v>
       </c>
       <c r="Q40" s="2" t="n">
         <v>27348</v>
@@ -3837,14 +3523,6 @@
       <c r="S40" t="n">
         <v>0.035</v>
       </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U40" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3911,7 +3589,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1497.57</v>
+        <v>1446.93</v>
       </c>
       <c r="Q41" s="2" t="n">
         <v>36701</v>
@@ -3922,14 +3600,6 @@
       <c r="S41" t="n">
         <v>0.035</v>
       </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U41" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3996,7 +3666,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1565.06</v>
+        <v>1512.14</v>
       </c>
       <c r="Q42" s="2" t="n">
         <v>26547</v>
@@ -4007,14 +3677,6 @@
       <c r="S42" t="n">
         <v>0.035</v>
       </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U42" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4077,7 +3739,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2100.67</v>
+        <v>2029.63</v>
       </c>
       <c r="Q43" s="2" t="n">
         <v>21710</v>
@@ -4088,14 +3750,6 @@
       <c r="S43" t="n">
         <v>0.035</v>
       </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U43" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4162,7 +3816,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2467.03</v>
+        <v>2383.6</v>
       </c>
       <c r="Q44" s="2" t="n">
         <v>30478</v>
@@ -4173,14 +3827,6 @@
       <c r="S44" t="n">
         <v>0.035</v>
       </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U44" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4247,7 +3893,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1742.88</v>
+        <v>1683.94</v>
       </c>
       <c r="Q45" s="2" t="n">
         <v>32630</v>
@@ -4258,14 +3904,6 @@
       <c r="S45" t="n">
         <v>0.035</v>
       </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U45" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4332,7 +3970,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2101.74</v>
+        <v>2030.67</v>
       </c>
       <c r="Q46" s="2" t="n">
         <v>37170</v>
@@ -4343,14 +3981,6 @@
       <c r="S46" t="n">
         <v>0.035</v>
       </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U46" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4417,7 +4047,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1483.65</v>
+        <v>1433.48</v>
       </c>
       <c r="Q47" s="2" t="n">
         <v>31389</v>
@@ -4428,14 +4058,6 @@
       <c r="S47" t="n">
         <v>0.035</v>
       </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U47" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4502,7 +4124,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1431.16</v>
+        <v>1382.76</v>
       </c>
       <c r="Q48" s="2" t="n">
         <v>22684</v>
@@ -4513,14 +4135,6 @@
       <c r="S48" t="n">
         <v>0.035</v>
       </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U48" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4587,7 +4201,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1613.26</v>
+        <v>1558.71</v>
       </c>
       <c r="Q49" s="2" t="n">
         <v>33549</v>
@@ -4598,14 +4212,6 @@
       <c r="S49" t="n">
         <v>0.035</v>
       </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U49" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4672,7 +4278,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1228.69</v>
+        <v>1187.14</v>
       </c>
       <c r="Q50" s="2" t="n">
         <v>37153</v>
@@ -4683,14 +4289,6 @@
       <c r="S50" t="n">
         <v>0.035</v>
       </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U50" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4757,7 +4355,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1587.56</v>
+        <v>1533.87</v>
       </c>
       <c r="Q51" s="2" t="n">
         <v>25522</v>
@@ -4768,14 +4366,6 @@
       <c r="S51" t="n">
         <v>0.035</v>
       </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U51" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4842,7 +4432,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1467.58</v>
+        <v>1417.95</v>
       </c>
       <c r="Q52" s="2" t="n">
         <v>35261</v>
@@ -4853,14 +4443,6 @@
       <c r="S52" t="n">
         <v>0.035</v>
       </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U52" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4927,7 +4509,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1360.46</v>
+        <v>1314.45</v>
       </c>
       <c r="Q53" s="2" t="n">
         <v>30031</v>
@@ -4938,14 +4520,6 @@
       <c r="S53" t="n">
         <v>0.035</v>
       </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U53" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5012,7 +4586,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2103.89</v>
+        <v>2032.74</v>
       </c>
       <c r="Q54" s="2" t="n">
         <v>30657</v>
@@ -5023,14 +4597,6 @@
       <c r="S54" t="n">
         <v>0.035</v>
       </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U54" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5097,7 +4663,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2238.86</v>
+        <v>2163.15</v>
       </c>
       <c r="Q55" s="2" t="n">
         <v>23508</v>
@@ -5108,14 +4674,6 @@
       <c r="S55" t="n">
         <v>0.035</v>
       </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U55" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5182,7 +4740,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1778.23</v>
+        <v>1718.1</v>
       </c>
       <c r="Q56" s="2" t="n">
         <v>29406</v>
@@ -5193,14 +4751,6 @@
       <c r="S56" t="n">
         <v>0.035</v>
       </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U56" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5267,7 +4817,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1711.82</v>
+        <v>1653.93</v>
       </c>
       <c r="Q57" s="2" t="n">
         <v>23174</v>
@@ -5278,14 +4828,6 @@
       <c r="S57" t="n">
         <v>0.035</v>
       </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U57" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5352,7 +4894,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2123.17</v>
+        <v>2051.37</v>
       </c>
       <c r="Q58" s="2" t="n">
         <v>18274</v>
@@ -5363,14 +4905,6 @@
       <c r="S58" t="n">
         <v>0.035</v>
       </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U58" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5437,7 +4971,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2414.54</v>
+        <v>2332.89</v>
       </c>
       <c r="Q59" s="2" t="n">
         <v>32827</v>
@@ -5448,14 +4982,6 @@
       <c r="S59" t="n">
         <v>0.035</v>
       </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U59" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5522,7 +5048,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1912.14</v>
+        <v>1847.48</v>
       </c>
       <c r="Q60" s="2" t="n">
         <v>35963</v>
@@ -5533,14 +5059,6 @@
       <c r="S60" t="n">
         <v>0.035</v>
       </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U60" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5607,7 +5125,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1470.79</v>
+        <v>1421.05</v>
       </c>
       <c r="Q61" s="2" t="n">
         <v>26104</v>
@@ -5618,14 +5136,6 @@
       <c r="S61" t="n">
         <v>0.035</v>
       </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U61" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5692,7 +5202,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1336.89</v>
+        <v>1291.68</v>
       </c>
       <c r="Q62" s="2" t="n">
         <v>22943</v>
@@ -5703,14 +5213,6 @@
       <c r="S62" t="n">
         <v>0.035</v>
       </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U62" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5777,7 +5279,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2077.1</v>
+        <v>2006.86</v>
       </c>
       <c r="Q63" s="2" t="n">
         <v>25926</v>
@@ -5788,14 +5290,6 @@
       <c r="S63" t="n">
         <v>0.035</v>
       </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U63" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5862,7 +5356,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2009.62</v>
+        <v>1941.66</v>
       </c>
       <c r="Q64" s="2" t="n">
         <v>23769</v>
@@ -5873,14 +5367,6 @@
       <c r="S64" t="n">
         <v>0.035</v>
       </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U64" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5947,7 +5433,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1414.02</v>
+        <v>1366.2</v>
       </c>
       <c r="Q65" s="2" t="n">
         <v>34125</v>
@@ -5958,14 +5444,6 @@
       <c r="S65" t="n">
         <v>0.035</v>
       </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U65" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6032,7 +5510,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1877.85</v>
+        <v>1814.35</v>
       </c>
       <c r="Q66" s="2" t="n">
         <v>27288</v>
@@ -6043,14 +5521,6 @@
       <c r="S66" t="n">
         <v>0.035</v>
       </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U66" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6117,7 +5587,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2127.45</v>
+        <v>2055.51</v>
       </c>
       <c r="Q67" s="2" t="n">
         <v>20738</v>
@@ -6128,14 +5598,6 @@
       <c r="S67" t="n">
         <v>0.035</v>
       </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U67" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6202,7 +5664,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1508.28</v>
+        <v>1457.28</v>
       </c>
       <c r="Q68" s="2" t="n">
         <v>24801</v>
@@ -6213,14 +5675,6 @@
       <c r="S68" t="n">
         <v>0.035</v>
       </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U68" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6287,7 +5741,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1253.33</v>
+        <v>1210.95</v>
       </c>
       <c r="Q69" s="2" t="n">
         <v>37411</v>
@@ -6298,14 +5752,6 @@
       <c r="S69" t="n">
         <v>0.035</v>
       </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U69" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6372,7 +5818,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1546.85</v>
+        <v>1494.54</v>
       </c>
       <c r="Q70" s="2" t="n">
         <v>23273</v>
@@ -6383,14 +5829,6 @@
       <c r="S70" t="n">
         <v>0.035</v>
       </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U70" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6457,7 +5895,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1781.44</v>
+        <v>1721.2</v>
       </c>
       <c r="Q71" s="2" t="n">
         <v>31640</v>
@@ -6468,14 +5906,6 @@
       <c r="S71" t="n">
         <v>0.035</v>
       </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U71" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6538,7 +5968,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1665.75</v>
+        <v>1609.42</v>
       </c>
       <c r="Q72" s="2" t="n">
         <v>30773</v>
@@ -6549,14 +5979,6 @@
       <c r="S72" t="n">
         <v>0.035</v>
       </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U72" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6623,7 +6045,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2413.48</v>
+        <v>2331.86</v>
       </c>
       <c r="Q73" s="2" t="n">
         <v>18609</v>
@@ -6634,14 +6056,6 @@
       <c r="S73" t="n">
         <v>0.035</v>
       </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U73" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6708,7 +6122,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2211.01</v>
+        <v>2136.24</v>
       </c>
       <c r="Q74" s="2" t="n">
         <v>29396</v>
@@ -6719,14 +6133,6 @@
       <c r="S74" t="n">
         <v>0.035</v>
       </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U74" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6793,7 +6199,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1862.86</v>
+        <v>1799.86</v>
       </c>
       <c r="Q75" s="2" t="n">
         <v>31619</v>
@@ -6804,14 +6210,6 @@
       <c r="S75" t="n">
         <v>0.035</v>
       </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U75" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6878,7 +6276,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1838.22</v>
+        <v>1776.06</v>
       </c>
       <c r="Q76" s="2" t="n">
         <v>29007</v>
@@ -6889,14 +6287,6 @@
       <c r="S76" t="n">
         <v>0.035</v>
       </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U76" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6959,7 +6349,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1539.35</v>
+        <v>1487.29</v>
       </c>
       <c r="Q77" s="2" t="n">
         <v>23979</v>
@@ -6970,14 +6360,6 @@
       <c r="S77" t="n">
         <v>0.035</v>
       </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U77" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7044,7 +6426,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1562.91</v>
+        <v>1510.06</v>
       </c>
       <c r="Q78" s="2" t="n">
         <v>33045</v>
@@ -7055,14 +6437,6 @@
       <c r="S78" t="n">
         <v>0.035</v>
       </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U78" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7129,7 +6503,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1607.91</v>
+        <v>1553.54</v>
       </c>
       <c r="Q79" s="2" t="n">
         <v>36516</v>
@@ -7140,14 +6514,6 @@
       <c r="S79" t="n">
         <v>0.035</v>
       </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U79" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7214,7 +6580,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1446.15</v>
+        <v>1397.25</v>
       </c>
       <c r="Q80" s="2" t="n">
         <v>21286</v>
@@ -7225,14 +6591,6 @@
       <c r="S80" t="n">
         <v>0.035</v>
       </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U80" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7299,7 +6657,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1492.22</v>
+        <v>1441.76</v>
       </c>
       <c r="Q81" s="2" t="n">
         <v>19392</v>
@@ -7310,14 +6668,6 @@
       <c r="S81" t="n">
         <v>0.035</v>
       </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U81" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7384,7 +6734,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2342.76</v>
+        <v>2263.54</v>
       </c>
       <c r="Q82" s="2" t="n">
         <v>37126</v>
@@ -7395,14 +6745,6 @@
       <c r="S82" t="n">
         <v>0.035</v>
       </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U82" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7469,7 +6811,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2171.37</v>
+        <v>2097.94</v>
       </c>
       <c r="Q83" s="2" t="n">
         <v>34154</v>
@@ -7480,14 +6822,6 @@
       <c r="S83" t="n">
         <v>0.035</v>
       </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U83" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7554,7 +6888,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1660.4</v>
+        <v>1604.25</v>
       </c>
       <c r="Q84" s="2" t="n">
         <v>27108</v>
@@ -7565,14 +6899,6 @@
       <c r="S84" t="n">
         <v>0.035</v>
       </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U84" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7639,7 +6965,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1412.94</v>
+        <v>1365.16</v>
       </c>
       <c r="Q85" s="2" t="n">
         <v>20935</v>
@@ -7650,14 +6976,6 @@
       <c r="S85" t="n">
         <v>0.035</v>
       </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U85" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7724,7 +7042,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2102.81</v>
+        <v>2031.7</v>
       </c>
       <c r="Q86" s="2" t="n">
         <v>27379</v>
@@ -7735,14 +7053,6 @@
       <c r="S86" t="n">
         <v>0.035</v>
       </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U86" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7809,7 +7119,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2021.4</v>
+        <v>1953.04</v>
       </c>
       <c r="Q87" s="2" t="n">
         <v>28135</v>
@@ -7820,14 +7130,6 @@
       <c r="S87" t="n">
         <v>0.035</v>
       </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U87" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7894,7 +7196,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1629.34</v>
+        <v>1574.24</v>
       </c>
       <c r="Q88" s="2" t="n">
         <v>34651</v>
@@ -7905,14 +7207,6 @@
       <c r="S88" t="n">
         <v>0.035</v>
       </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U88" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7979,7 +7273,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1785.73</v>
+        <v>1725.34</v>
       </c>
       <c r="Q89" s="2" t="n">
         <v>26665</v>
@@ -7990,14 +7284,6 @@
       <c r="S89" t="n">
         <v>0.035</v>
       </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U89" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8064,7 +7350,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1793.23</v>
+        <v>1732.59</v>
       </c>
       <c r="Q90" s="2" t="n">
         <v>33031</v>
@@ -8075,14 +7361,6 @@
       <c r="S90" t="n">
         <v>0.035</v>
       </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U90" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8149,7 +7427,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2276.36</v>
+        <v>2199.38</v>
       </c>
       <c r="Q91" s="2" t="n">
         <v>24614</v>
@@ -8160,14 +7438,6 @@
       <c r="S91" t="n">
         <v>0.035</v>
       </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U91" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8234,7 +7504,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1636.83</v>
+        <v>1581.48</v>
       </c>
       <c r="Q92" s="2" t="n">
         <v>32096</v>
@@ -8245,14 +7515,6 @@
       <c r="S92" t="n">
         <v>0.035</v>
       </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U92" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8319,7 +7581,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1944.27</v>
+        <v>1878.52</v>
       </c>
       <c r="Q93" s="2" t="n">
         <v>37332</v>
@@ -8330,14 +7592,6 @@
       <c r="S93" t="n">
         <v>0.035</v>
       </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U93" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8404,7 +7658,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1818.94</v>
+        <v>1757.43</v>
       </c>
       <c r="Q94" s="2" t="n">
         <v>33136</v>
@@ -8415,14 +7669,6 @@
       <c r="S94" t="n">
         <v>0.035</v>
       </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U94" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8485,7 +7731,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2287.06</v>
+        <v>2209.72</v>
       </c>
       <c r="Q95" s="2" t="n">
         <v>22937</v>
@@ -8496,14 +7742,6 @@
       <c r="S95" t="n">
         <v>0.035</v>
       </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U95" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8570,7 +7808,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1599.34</v>
+        <v>1545.26</v>
       </c>
       <c r="Q96" s="2" t="n">
         <v>18833</v>
@@ -8581,14 +7819,6 @@
       <c r="S96" t="n">
         <v>0.035</v>
       </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U96" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8655,7 +7885,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2239.93</v>
+        <v>2164.18</v>
       </c>
       <c r="Q97" s="2" t="n">
         <v>20047</v>
@@ -8666,14 +7896,6 @@
       <c r="S97" t="n">
         <v>0.035</v>
       </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U97" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8740,23 +7962,15 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2292.42</v>
+        <v>2214.9</v>
       </c>
       <c r="Q98" s="2" t="n">
         <v>23431</v>
       </c>
       <c r="R98" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S98" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U98" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -8825,7 +8039,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2380.26</v>
+        <v>2299.77</v>
       </c>
       <c r="Q99" s="2" t="n">
         <v>23818</v>
@@ -8836,14 +8050,6 @@
       <c r="S99" t="n">
         <v>0.035</v>
       </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U99" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8910,7 +8116,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1410.8</v>
+        <v>1363.09</v>
       </c>
       <c r="Q100" s="2" t="n">
         <v>33834</v>
@@ -8921,14 +8127,6 @@
       <c r="S100" t="n">
         <v>0.035</v>
       </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U100" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8995,7 +8193,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1304.75</v>
+        <v>1260.63</v>
       </c>
       <c r="Q101" s="2" t="n">
         <v>28632</v>
@@ -9006,14 +8204,6 @@
       <c r="S101" t="n">
         <v>0.035</v>
       </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U101" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9080,7 +8270,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1977.48</v>
+        <v>1910.61</v>
       </c>
       <c r="Q102" s="2" t="n">
         <v>28679</v>
@@ -9091,14 +8281,6 @@
       <c r="S102" t="n">
         <v>0.035</v>
       </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U102" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9165,7 +8347,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1480.43</v>
+        <v>1430.37</v>
       </c>
       <c r="Q103" s="2" t="n">
         <v>33395</v>
@@ -9176,14 +8358,6 @@
       <c r="S103" t="n">
         <v>0.035</v>
       </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U103" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9250,7 +8424,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1741.81</v>
+        <v>1682.91</v>
       </c>
       <c r="Q104" s="2" t="n">
         <v>22565</v>
@@ -9261,14 +8435,6 @@
       <c r="S104" t="n">
         <v>0.035</v>
       </c>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U104" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9335,7 +8501,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1515.78</v>
+        <v>1464.52</v>
       </c>
       <c r="Q105" s="2" t="n">
         <v>21068</v>
@@ -9346,14 +8512,6 @@
       <c r="S105" t="n">
         <v>0.035</v>
       </c>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U105" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9420,7 +8578,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1672.18</v>
+        <v>1615.63</v>
       </c>
       <c r="Q106" s="2" t="n">
         <v>21615</v>
@@ -9431,14 +8589,6 @@
       <c r="S106" t="n">
         <v>0.035</v>
       </c>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U106" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9505,7 +8655,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1734.31</v>
+        <v>1675.66</v>
       </c>
       <c r="Q107" s="2" t="n">
         <v>23932</v>
@@ -9516,14 +8666,6 @@
       <c r="S107" t="n">
         <v>0.035</v>
       </c>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U107" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9590,7 +8732,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1889.64</v>
+        <v>1825.74</v>
       </c>
       <c r="Q108" s="2" t="n">
         <v>31405</v>
@@ -9601,14 +8743,6 @@
       <c r="S108" t="n">
         <v>0.035</v>
       </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U108" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9675,7 +8809,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1469.72</v>
+        <v>1420.02</v>
       </c>
       <c r="Q109" s="2" t="n">
         <v>21665</v>
@@ -9686,14 +8820,6 @@
       <c r="S109" t="n">
         <v>0.035</v>
       </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U109" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9760,7 +8886,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1885.36</v>
+        <v>1821.6</v>
       </c>
       <c r="Q110" s="2" t="n">
         <v>37809</v>
@@ -9771,14 +8897,6 @@
       <c r="S110" t="n">
         <v>0.035</v>
       </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U110" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9845,7 +8963,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1532.92</v>
+        <v>1481.08</v>
       </c>
       <c r="Q111" s="2" t="n">
         <v>18494</v>
@@ -9856,14 +8974,6 @@
       <c r="S111" t="n">
         <v>0.035</v>
       </c>
-      <c r="T111" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U111" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9930,7 +9040,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1705.39</v>
+        <v>1647.72</v>
       </c>
       <c r="Q112" s="2" t="n">
         <v>26402</v>
@@ -9941,14 +9051,6 @@
       <c r="S112" t="n">
         <v>0.035</v>
       </c>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U112" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10015,7 +9117,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1557.56</v>
+        <v>1504.89</v>
       </c>
       <c r="Q113" s="2" t="n">
         <v>29271</v>
@@ -10026,14 +9128,6 @@
       <c r="S113" t="n">
         <v>0.035</v>
       </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U113" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10100,7 +9194,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1890.72</v>
+        <v>1826.78</v>
       </c>
       <c r="Q114" s="2" t="n">
         <v>25587</v>
@@ -10111,14 +9205,6 @@
       <c r="S114" t="n">
         <v>0.035</v>
       </c>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U114" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10185,7 +9271,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1512.57</v>
+        <v>1461.42</v>
       </c>
       <c r="Q115" s="2" t="n">
         <v>27899</v>
@@ -10196,14 +9282,6 @@
       <c r="S115" t="n">
         <v>0.035</v>
       </c>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U115" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10270,7 +9348,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1569.35</v>
+        <v>1516.28</v>
       </c>
       <c r="Q116" s="2" t="n">
         <v>18348</v>
@@ -10281,14 +9359,6 @@
       <c r="S116" t="n">
         <v>0.035</v>
       </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U116" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10355,7 +9425,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>1760.02</v>
+        <v>1700.5</v>
       </c>
       <c r="Q117" s="2" t="n">
         <v>26850</v>
@@ -10366,14 +9436,6 @@
       <c r="S117" t="n">
         <v>0.035</v>
       </c>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U117" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10440,7 +9502,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1454.72</v>
+        <v>1405.53</v>
       </c>
       <c r="Q118" s="2" t="n">
         <v>25524</v>
@@ -10451,14 +9513,6 @@
       <c r="S118" t="n">
         <v>0.035</v>
       </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U118" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10525,7 +9579,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1429.01</v>
+        <v>1380.69</v>
       </c>
       <c r="Q119" s="2" t="n">
         <v>36003</v>
@@ -10536,14 +9590,6 @@
       <c r="S119" t="n">
         <v>0.035</v>
       </c>
-      <c r="T119" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U119" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10610,7 +9656,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>1818.94</v>
+        <v>1757.43</v>
       </c>
       <c r="Q120" s="2" t="n">
         <v>36850</v>
@@ -10621,14 +9667,6 @@
       <c r="S120" t="n">
         <v>0.035</v>
       </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U120" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10695,7 +9733,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2283.85</v>
+        <v>2206.62</v>
       </c>
       <c r="Q121" s="2" t="n">
         <v>37606</v>
@@ -10706,14 +9744,6 @@
       <c r="S121" t="n">
         <v>0.035</v>
       </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U121" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10780,7 +9810,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2330.99</v>
+        <v>2252.16</v>
       </c>
       <c r="Q122" s="2" t="n">
         <v>34474</v>
@@ -10791,14 +9821,6 @@
       <c r="S122" t="n">
         <v>0.035</v>
       </c>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U122" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10865,23 +9887,15 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1692.54</v>
+        <v>1635.3</v>
       </c>
       <c r="Q123" s="2" t="n">
         <v>36214</v>
       </c>
       <c r="R123" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S123" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="T123" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U123" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -10950,7 +9964,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1980.7</v>
+        <v>1913.72</v>
       </c>
       <c r="Q124" s="2" t="n">
         <v>35111</v>
@@ -10961,14 +9975,6 @@
       <c r="S124" t="n">
         <v>0.035</v>
       </c>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U124" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11035,7 +10041,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2191.73</v>
+        <v>2117.61</v>
       </c>
       <c r="Q125" s="2" t="n">
         <v>18751</v>
@@ -11046,14 +10052,6 @@
       <c r="S125" t="n">
         <v>0.035</v>
       </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U125" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11120,7 +10118,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1915.35</v>
+        <v>1850.58</v>
       </c>
       <c r="Q126" s="2" t="n">
         <v>35908</v>
@@ -11131,14 +10129,6 @@
       <c r="S126" t="n">
         <v>0.035</v>
       </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U126" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11205,7 +10195,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>2128.52</v>
+        <v>2056.54</v>
       </c>
       <c r="Q127" s="2" t="n">
         <v>25707</v>
@@ -11216,14 +10206,6 @@
       <c r="S127" t="n">
         <v>0.035</v>
       </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U127" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11290,7 +10272,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2159.59</v>
+        <v>2086.56</v>
       </c>
       <c r="Q128" s="2" t="n">
         <v>19352</v>
@@ -11301,14 +10283,6 @@
       <c r="S128" t="n">
         <v>0.035</v>
       </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U128" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11375,7 +10349,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1816.8</v>
+        <v>1755.36</v>
       </c>
       <c r="Q129" s="2" t="n">
         <v>24794</v>
@@ -11386,14 +10360,6 @@
       <c r="S129" t="n">
         <v>0.035</v>
       </c>
-      <c r="T129" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U129" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11460,7 +10426,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2283.85</v>
+        <v>2206.62</v>
       </c>
       <c r="Q130" s="2" t="n">
         <v>24313</v>
@@ -11471,14 +10437,6 @@
       <c r="S130" t="n">
         <v>0.035</v>
       </c>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U130" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11545,7 +10503,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1946.41</v>
+        <v>1880.59</v>
       </c>
       <c r="Q131" s="2" t="n">
         <v>27376</v>
@@ -11556,14 +10514,6 @@
       <c r="S131" t="n">
         <v>0.035</v>
       </c>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U131" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11630,7 +10580,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1818.94</v>
+        <v>1757.43</v>
       </c>
       <c r="Q132" s="2" t="n">
         <v>25579</v>
@@ -11641,14 +10591,6 @@
       <c r="S132" t="n">
         <v>0.035</v>
       </c>
-      <c r="T132" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U132" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11715,7 +10657,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1953.91</v>
+        <v>1887.84</v>
       </c>
       <c r="Q133" s="2" t="n">
         <v>26870</v>
@@ -11726,14 +10668,6 @@
       <c r="S133" t="n">
         <v>0.035</v>
       </c>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U133" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11796,7 +10730,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1752.52</v>
+        <v>1693.26</v>
       </c>
       <c r="Q134" s="2" t="n">
         <v>36326</v>
@@ -11807,14 +10741,6 @@
       <c r="S134" t="n">
         <v>0.035</v>
       </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U134" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11881,7 +10807,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1454.72</v>
+        <v>1405.53</v>
       </c>
       <c r="Q135" s="2" t="n">
         <v>33873</v>
@@ -11892,14 +10818,6 @@
       <c r="S135" t="n">
         <v>0.035</v>
       </c>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U135" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11966,7 +10884,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2104.96</v>
+        <v>2033.78</v>
       </c>
       <c r="Q136" s="2" t="n">
         <v>32331</v>
@@ -11977,14 +10895,6 @@
       <c r="S136" t="n">
         <v>0.035</v>
       </c>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U136" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12051,7 +10961,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1440.79</v>
+        <v>1392.07</v>
       </c>
       <c r="Q137" s="2" t="n">
         <v>22421</v>
@@ -12062,14 +10972,6 @@
       <c r="S137" t="n">
         <v>0.035</v>
       </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U137" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12136,7 +11038,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1447.22</v>
+        <v>1398.28</v>
       </c>
       <c r="Q138" s="2" t="n">
         <v>27388</v>
@@ -12147,14 +11049,6 @@
       <c r="S138" t="n">
         <v>0.035</v>
       </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U138" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12221,7 +11115,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2265.64</v>
+        <v>2189.02</v>
       </c>
       <c r="Q139" s="2" t="n">
         <v>32762</v>
@@ -12232,14 +11126,6 @@
       <c r="S139" t="n">
         <v>0.035</v>
       </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U139" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12306,7 +11192,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1883.21</v>
+        <v>1819.53</v>
       </c>
       <c r="Q140" s="2" t="n">
         <v>30052</v>
@@ -12317,14 +11203,6 @@
       <c r="S140" t="n">
         <v>0.035</v>
       </c>
-      <c r="T140" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U140" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12391,7 +11269,7 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>1471.86</v>
+        <v>1422.09</v>
       </c>
       <c r="Q141" s="2" t="n">
         <v>25362</v>
@@ -12402,14 +11280,6 @@
       <c r="S141" t="n">
         <v>0.035</v>
       </c>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U141" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12476,7 +11346,7 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>2111.38</v>
+        <v>2039.98</v>
       </c>
       <c r="Q142" s="2" t="n">
         <v>36389</v>
@@ -12487,14 +11357,6 @@
       <c r="S142" t="n">
         <v>0.035</v>
       </c>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U142" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12561,7 +11423,7 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>1448.3</v>
+        <v>1399.32</v>
       </c>
       <c r="Q143" s="2" t="n">
         <v>34268</v>
@@ -12572,14 +11434,6 @@
       <c r="S143" t="n">
         <v>0.035</v>
       </c>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U143" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12642,7 +11496,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2158.51</v>
+        <v>2085.52</v>
       </c>
       <c r="Q144" s="2" t="n">
         <v>27321</v>
@@ -12653,14 +11507,6 @@
       <c r="S144" t="n">
         <v>0.035</v>
       </c>
-      <c r="T144" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U144" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12727,7 +11573,7 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2249.57</v>
+        <v>2173.5</v>
       </c>
       <c r="Q145" s="2" t="n">
         <v>21595</v>
@@ -12738,14 +11584,6 @@
       <c r="S145" t="n">
         <v>0.035</v>
       </c>
-      <c r="T145" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U145" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12812,7 +11650,7 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1787.88</v>
+        <v>1727.42</v>
       </c>
       <c r="Q146" s="2" t="n">
         <v>20645</v>
@@ -12823,14 +11661,6 @@
       <c r="S146" t="n">
         <v>0.035</v>
       </c>
-      <c r="T146" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U146" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12897,7 +11727,7 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2066.4</v>
+        <v>1996.52</v>
       </c>
       <c r="Q147" s="2" t="n">
         <v>26795</v>
@@ -12908,14 +11738,6 @@
       <c r="S147" t="n">
         <v>0.035</v>
       </c>
-      <c r="T147" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U147" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12982,7 +11804,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2110.31</v>
+        <v>2038.95</v>
       </c>
       <c r="Q148" s="2" t="n">
         <v>31087</v>
@@ -12993,14 +11815,6 @@
       <c r="S148" t="n">
         <v>0.035</v>
       </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U148" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13067,7 +11881,7 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1630.4</v>
+        <v>1575.27</v>
       </c>
       <c r="Q149" s="2" t="n">
         <v>33056</v>
@@ -13078,14 +11892,6 @@
       <c r="S149" t="n">
         <v>0.035</v>
       </c>
-      <c r="T149" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U149" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -13152,7 +11958,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>1601.48</v>
+        <v>1547.32</v>
       </c>
       <c r="Q150" s="2" t="n">
         <v>33459</v>
@@ -13163,14 +11969,6 @@
       <c r="S150" t="n">
         <v>0.035</v>
       </c>
-      <c r="T150" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U150" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13237,7 +12035,7 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1464.36</v>
+        <v>1414.84</v>
       </c>
       <c r="Q151" s="2" t="n">
         <v>23662</v>
@@ -13248,14 +12046,6 @@
       <c r="S151" t="n">
         <v>0.035</v>
       </c>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U151" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13322,7 +12112,7 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1931.41</v>
+        <v>1866.1</v>
       </c>
       <c r="Q152" s="2" t="n">
         <v>34428</v>
@@ -13333,14 +12123,6 @@
       <c r="S152" t="n">
         <v>0.035</v>
       </c>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U152" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -13407,7 +12189,7 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1262.97</v>
+        <v>1220.26</v>
       </c>
       <c r="Q153" s="2" t="n">
         <v>30793</v>
@@ -13418,14 +12200,6 @@
       <c r="S153" t="n">
         <v>0.035</v>
       </c>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U153" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -13492,7 +12266,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>2214.22</v>
+        <v>2139.34</v>
       </c>
       <c r="Q154" s="2" t="n">
         <v>36821</v>
@@ -13503,14 +12277,6 @@
       <c r="S154" t="n">
         <v>0.035</v>
       </c>
-      <c r="T154" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U154" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -13577,7 +12343,7 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1811.44</v>
+        <v>1750.18</v>
       </c>
       <c r="Q155" s="2" t="n">
         <v>20345</v>
@@ -13588,14 +12354,6 @@
       <c r="S155" t="n">
         <v>0.035</v>
       </c>
-      <c r="T155" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U155" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -13662,7 +12420,7 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2004.26</v>
+        <v>1936.48</v>
       </c>
       <c r="Q156" s="2" t="n">
         <v>33741</v>
@@ -13673,14 +12431,6 @@
       <c r="S156" t="n">
         <v>0.035</v>
       </c>
-      <c r="T156" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U156" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -13747,7 +12497,7 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1751.45</v>
+        <v>1692.22</v>
       </c>
       <c r="Q157" s="2" t="n">
         <v>30896</v>
@@ -13758,14 +12508,6 @@
       <c r="S157" t="n">
         <v>0.035</v>
       </c>
-      <c r="T157" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U157" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -13832,7 +12574,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2058.89</v>
+        <v>1989.27</v>
       </c>
       <c r="Q158" s="2" t="n">
         <v>27905</v>
@@ -13843,14 +12585,6 @@
       <c r="S158" t="n">
         <v>0.035</v>
       </c>
-      <c r="T158" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U158" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -13917,7 +12651,7 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>2043.9</v>
+        <v>1974.78</v>
       </c>
       <c r="Q159" s="2" t="n">
         <v>21209</v>
@@ -13928,14 +12662,6 @@
       <c r="S159" t="n">
         <v>0.035</v>
       </c>
-      <c r="T159" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U159" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14002,7 +12728,7 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>1395.8</v>
+        <v>1348.6</v>
       </c>
       <c r="Q160" s="2" t="n">
         <v>23393</v>
@@ -14013,14 +12739,6 @@
       <c r="S160" t="n">
         <v>0.035</v>
       </c>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U160" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -14087,7 +12805,7 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>1544.71</v>
+        <v>1492.47</v>
       </c>
       <c r="Q161" s="2" t="n">
         <v>27492</v>
@@ -14098,14 +12816,6 @@
       <c r="S161" t="n">
         <v>0.035</v>
       </c>
-      <c r="T161" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U161" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -14172,7 +12882,7 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2249.57</v>
+        <v>2173.5</v>
       </c>
       <c r="Q162" s="2" t="n">
         <v>36514</v>
@@ -14183,14 +12893,6 @@
       <c r="S162" t="n">
         <v>0.035</v>
       </c>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U162" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -14257,7 +12959,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>1230.83</v>
+        <v>1189.21</v>
       </c>
       <c r="Q163" s="2" t="n">
         <v>34498</v>
@@ -14268,14 +12970,6 @@
       <c r="S163" t="n">
         <v>0.035</v>
       </c>
-      <c r="T163" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U163" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -14342,7 +13036,7 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>1313.32</v>
+        <v>1268.91</v>
       </c>
       <c r="Q164" s="2" t="n">
         <v>35572</v>
@@ -14353,14 +13047,6 @@
       <c r="S164" t="n">
         <v>0.035</v>
       </c>
-      <c r="T164" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U164" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -14427,7 +13113,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2198.15</v>
+        <v>2123.82</v>
       </c>
       <c r="Q165" s="2" t="n">
         <v>35130</v>
@@ -14438,14 +13124,6 @@
       <c r="S165" t="n">
         <v>0.035</v>
       </c>
-      <c r="T165" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U165" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -14512,7 +13190,7 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>1550.06</v>
+        <v>1497.64</v>
       </c>
       <c r="Q166" s="2" t="n">
         <v>28778</v>
@@ -14523,14 +13201,6 @@
       <c r="S166" t="n">
         <v>0.035</v>
       </c>
-      <c r="T166" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U166" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -14597,7 +13267,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>2352.41</v>
+        <v>2272.86</v>
       </c>
       <c r="Q167" s="2" t="n">
         <v>27577</v>
@@ -14608,14 +13278,6 @@
       <c r="S167" t="n">
         <v>0.035</v>
       </c>
-      <c r="T167" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U167" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -14682,7 +13344,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>1499.72</v>
+        <v>1449</v>
       </c>
       <c r="Q168" s="2" t="n">
         <v>32640</v>
@@ -14693,14 +13355,6 @@
       <c r="S168" t="n">
         <v>0.035</v>
       </c>
-      <c r="T168" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U168" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -14767,7 +13421,7 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>2199.23</v>
+        <v>2124.86</v>
       </c>
       <c r="Q169" s="2" t="n">
         <v>28377</v>
@@ -14778,14 +13432,6 @@
       <c r="S169" t="n">
         <v>0.035</v>
       </c>
-      <c r="T169" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U169" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -14848,7 +13494,7 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>1533.99</v>
+        <v>1482.12</v>
       </c>
       <c r="Q170" s="2" t="n">
         <v>38561</v>
@@ -14859,14 +13505,6 @@
       <c r="S170" t="n">
         <v>0.035</v>
       </c>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U170" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -14933,7 +13571,7 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2098.52</v>
+        <v>2027.56</v>
       </c>
       <c r="Q171" s="2" t="n">
         <v>24121</v>
@@ -14944,14 +13582,6 @@
       <c r="S171" t="n">
         <v>0.035</v>
       </c>
-      <c r="T171" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U171" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -15018,7 +13648,7 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>2381.33</v>
+        <v>2300.8</v>
       </c>
       <c r="Q172" s="2" t="n">
         <v>35758</v>
@@ -15029,14 +13659,6 @@
       <c r="S172" t="n">
         <v>0.035</v>
       </c>
-      <c r="T172" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U172" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -15103,7 +13725,7 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>1659.33</v>
+        <v>1603.22</v>
       </c>
       <c r="Q173" s="2" t="n">
         <v>22933</v>
@@ -15114,14 +13736,6 @@
       <c r="S173" t="n">
         <v>0.035</v>
       </c>
-      <c r="T173" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U173" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -15188,7 +13802,7 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>1418.3</v>
+        <v>1370.34</v>
       </c>
       <c r="Q174" s="2" t="n">
         <v>27121</v>
@@ -15199,14 +13813,6 @@
       <c r="S174" t="n">
         <v>0.035</v>
       </c>
-      <c r="T174" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U174" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -15273,7 +13879,7 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>1883.21</v>
+        <v>1819.53</v>
       </c>
       <c r="Q175" s="2" t="n">
         <v>30727</v>
@@ -15284,14 +13890,6 @@
       <c r="S175" t="n">
         <v>0.035</v>
       </c>
-      <c r="T175" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U175" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -15358,7 +13956,7 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>1797.52</v>
+        <v>1736.73</v>
       </c>
       <c r="Q176" s="2" t="n">
         <v>23454</v>
@@ -15369,14 +13967,6 @@
       <c r="S176" t="n">
         <v>0.035</v>
       </c>
-      <c r="T176" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U176" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -15443,7 +14033,7 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>1270.47</v>
+        <v>1227.51</v>
       </c>
       <c r="Q177" s="2" t="n">
         <v>36232</v>
@@ -15454,14 +14044,6 @@
       <c r="S177" t="n">
         <v>0.035</v>
       </c>
-      <c r="T177" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U177" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -15524,7 +14106,7 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>1839.29</v>
+        <v>1777.09</v>
       </c>
       <c r="Q178" s="2" t="n">
         <v>27832</v>
@@ -15535,14 +14117,6 @@
       <c r="S178" t="n">
         <v>0.035</v>
       </c>
-      <c r="T178" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U178" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -15609,7 +14183,7 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>2280.64</v>
+        <v>2203.52</v>
       </c>
       <c r="Q179" s="2" t="n">
         <v>19104</v>
@@ -15620,14 +14194,6 @@
       <c r="S179" t="n">
         <v>0.035</v>
       </c>
-      <c r="T179" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U179" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -15694,7 +14260,7 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>1522.22</v>
+        <v>1470.74</v>
       </c>
       <c r="Q180" s="2" t="n">
         <v>22040</v>
@@ -15705,14 +14271,6 @@
       <c r="S180" t="n">
         <v>0.035</v>
       </c>
-      <c r="T180" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U180" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -15779,7 +14337,7 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>1396.88</v>
+        <v>1349.64</v>
       </c>
       <c r="Q181" s="2" t="n">
         <v>20383</v>
@@ -15790,14 +14348,6 @@
       <c r="S181" t="n">
         <v>0.035</v>
       </c>
-      <c r="T181" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U181" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -15864,7 +14414,7 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>1555.42</v>
+        <v>1502.82</v>
       </c>
       <c r="Q182" s="2" t="n">
         <v>34163</v>
@@ -15875,14 +14425,6 @@
       <c r="S182" t="n">
         <v>0.035</v>
       </c>
-      <c r="T182" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U182" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -15949,7 +14491,7 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1328.32</v>
+        <v>1283.4</v>
       </c>
       <c r="Q183" s="2" t="n">
         <v>20988</v>
@@ -15960,14 +14502,6 @@
       <c r="S183" t="n">
         <v>0.035</v>
       </c>
-      <c r="T183" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U183" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -16034,7 +14568,7 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>2005.33</v>
+        <v>1937.52</v>
       </c>
       <c r="Q184" s="2" t="n">
         <v>29660</v>
@@ -16045,14 +14579,6 @@
       <c r="S184" t="n">
         <v>0.035</v>
       </c>
-      <c r="T184" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U184" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -16119,7 +14645,7 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>2079.25</v>
+        <v>2008.94</v>
       </c>
       <c r="Q185" s="2" t="n">
         <v>29591</v>
@@ -16130,14 +14656,6 @@
       <c r="S185" t="n">
         <v>0.035</v>
       </c>
-      <c r="T185" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U185" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -16204,7 +14722,7 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>1924.99</v>
+        <v>1859.89</v>
       </c>
       <c r="Q186" s="2" t="n">
         <v>21231</v>
@@ -16215,14 +14733,6 @@
       <c r="S186" t="n">
         <v>0.035</v>
       </c>
-      <c r="T186" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U186" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -16289,7 +14799,7 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2302.06</v>
+        <v>2224.21</v>
       </c>
       <c r="Q187" s="2" t="n">
         <v>33167</v>
@@ -16300,14 +14810,6 @@
       <c r="S187" t="n">
         <v>0.035</v>
       </c>
-      <c r="T187" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U187" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -16374,7 +14876,7 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>1884.28</v>
+        <v>1820.56</v>
       </c>
       <c r="Q188" s="2" t="n">
         <v>27877</v>
@@ -16385,14 +14887,6 @@
       <c r="S188" t="n">
         <v>0.035</v>
       </c>
-      <c r="T188" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U188" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -16459,7 +14953,7 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>1513.65</v>
+        <v>1462.46</v>
       </c>
       <c r="Q189" s="2" t="n">
         <v>37814</v>
@@ -16470,14 +14964,6 @@
       <c r="S189" t="n">
         <v>0.035</v>
       </c>
-      <c r="T189" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U189" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -16544,7 +15030,7 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>2112.46</v>
+        <v>2041.02</v>
       </c>
       <c r="Q190" s="2" t="n">
         <v>36744</v>
@@ -16555,14 +15041,6 @@
       <c r="S190" t="n">
         <v>0.035</v>
       </c>
-      <c r="T190" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U190" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -16629,7 +15107,7 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>1981.77</v>
+        <v>1914.75</v>
       </c>
       <c r="Q191" s="2" t="n">
         <v>30013</v>
@@ -16640,14 +15118,6 @@
       <c r="S191" t="n">
         <v>0.035</v>
       </c>
-      <c r="T191" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U191" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -16714,7 +15184,7 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2444.54</v>
+        <v>2361.87</v>
       </c>
       <c r="Q192" s="2" t="n">
         <v>21027</v>
@@ -16725,14 +15195,6 @@
       <c r="S192" t="n">
         <v>0.035</v>
       </c>
-      <c r="T192" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U192" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -16799,7 +15261,7 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>1530.79</v>
+        <v>1479.02</v>
       </c>
       <c r="Q193" s="2" t="n">
         <v>18917</v>
@@ -16810,14 +15272,6 @@
       <c r="S193" t="n">
         <v>0.035</v>
       </c>
-      <c r="T193" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U193" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -16884,7 +15338,7 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1892.85</v>
+        <v>1828.84</v>
       </c>
       <c r="Q194" s="2" t="n">
         <v>18772</v>
@@ -16895,14 +15349,6 @@
       <c r="S194" t="n">
         <v>0.035</v>
       </c>
-      <c r="T194" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U194" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -16969,7 +15415,7 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>1370.09</v>
+        <v>1323.76</v>
       </c>
       <c r="Q195" s="2" t="n">
         <v>29301</v>
@@ -16980,14 +15426,6 @@
       <c r="S195" t="n">
         <v>0.035</v>
       </c>
-      <c r="T195" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U195" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -17054,7 +15492,7 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>1346.52</v>
+        <v>1300.99</v>
       </c>
       <c r="Q196" s="2" t="n">
         <v>32583</v>
@@ -17065,14 +15503,6 @@
       <c r="S196" t="n">
         <v>0.035</v>
       </c>
-      <c r="T196" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U196" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -17139,7 +15569,7 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1976.4</v>
+        <v>1909.57</v>
       </c>
       <c r="Q197" s="2" t="n">
         <v>29028</v>
@@ -17150,14 +15580,6 @@
       <c r="S197" t="n">
         <v>0.035</v>
       </c>
-      <c r="T197" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U197" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -17224,7 +15646,7 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>1382.95</v>
+        <v>1336.18</v>
       </c>
       <c r="Q198" s="2" t="n">
         <v>37555</v>
@@ -17235,14 +15657,6 @@
       <c r="S198" t="n">
         <v>0.035</v>
       </c>
-      <c r="T198" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U198" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -17309,7 +15723,7 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>1408.66</v>
+        <v>1361.02</v>
       </c>
       <c r="Q199" s="2" t="n">
         <v>24939</v>
@@ -17320,14 +15734,6 @@
       <c r="S199" t="n">
         <v>0.035</v>
       </c>
-      <c r="T199" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U199" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -17394,7 +15800,7 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>1450.44</v>
+        <v>1401.39</v>
       </c>
       <c r="Q200" s="2" t="n">
         <v>22054</v>
@@ -17405,14 +15811,6 @@
       <c r="S200" t="n">
         <v>0.035</v>
       </c>
-      <c r="T200" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U200" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -17479,7 +15877,7 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>1770.73</v>
+        <v>1710.85</v>
       </c>
       <c r="Q201" s="2" t="n">
         <v>34033</v>
@@ -17490,14 +15888,6 @@
       <c r="S201" t="n">
         <v>0.035</v>
       </c>
-      <c r="T201" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U201" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -17564,7 +15954,7 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>1261.9</v>
+        <v>1219.23</v>
       </c>
       <c r="Q202" s="2" t="n">
         <v>31586</v>
@@ -17575,14 +15965,6 @@
       <c r="S202" t="n">
         <v>0.035</v>
       </c>
-      <c r="T202" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U202" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -17649,7 +16031,7 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>1916.42</v>
+        <v>1851.61</v>
       </c>
       <c r="Q203" s="2" t="n">
         <v>22256</v>
@@ -17660,14 +16042,6 @@
       <c r="S203" t="n">
         <v>0.035</v>
       </c>
-      <c r="T203" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U203" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -17734,7 +16108,7 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>1680.76</v>
+        <v>1623.92</v>
       </c>
       <c r="Q204" s="2" t="n">
         <v>27700</v>
@@ -17745,14 +16119,6 @@
       <c r="S204" t="n">
         <v>0.035</v>
       </c>
-      <c r="T204" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U204" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -17819,7 +16185,7 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1392.59</v>
+        <v>1345.5</v>
       </c>
       <c r="Q205" s="2" t="n">
         <v>22988</v>
@@ -17830,14 +16196,6 @@
       <c r="S205" t="n">
         <v>0.035</v>
       </c>
-      <c r="T205" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U205" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -17904,7 +16262,7 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>2204.58</v>
+        <v>2130.03</v>
       </c>
       <c r="Q206" s="2" t="n">
         <v>38638</v>
@@ -17915,14 +16273,6 @@
       <c r="S206" t="n">
         <v>0.035</v>
       </c>
-      <c r="T206" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U206" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -17989,23 +16339,15 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>1384.02</v>
+        <v>1337.22</v>
       </c>
       <c r="Q207" s="2" t="n">
         <v>31467</v>
       </c>
       <c r="R207" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S207" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="T207" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U207" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -18074,7 +16416,7 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>1509.35</v>
+        <v>1458.31</v>
       </c>
       <c r="Q208" s="2" t="n">
         <v>21536</v>
@@ -18085,14 +16427,6 @@
       <c r="S208" t="n">
         <v>0.035</v>
       </c>
-      <c r="T208" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U208" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -18159,7 +16493,7 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>1913.21</v>
+        <v>1848.51</v>
       </c>
       <c r="Q209" s="2" t="n">
         <v>25307</v>
@@ -18170,14 +16504,6 @@
       <c r="S209" t="n">
         <v>0.035</v>
       </c>
-      <c r="T209" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U209" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -18244,7 +16570,7 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>1524.35</v>
+        <v>1472.8</v>
       </c>
       <c r="Q210" s="2" t="n">
         <v>25294</v>
@@ -18255,14 +16581,6 @@
       <c r="S210" t="n">
         <v>0.035</v>
       </c>
-      <c r="T210" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U210" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -18329,7 +16647,7 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>1746.1</v>
+        <v>1687.05</v>
       </c>
       <c r="Q211" s="2" t="n">
         <v>33505</v>
@@ -18340,14 +16658,6 @@
       <c r="S211" t="n">
         <v>0.035</v>
       </c>
-      <c r="T211" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U211" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -18414,7 +16724,7 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>1444.01</v>
+        <v>1395.18</v>
       </c>
       <c r="Q212" s="2" t="n">
         <v>35299</v>
@@ -18425,14 +16735,6 @@
       <c r="S212" t="n">
         <v>0.035</v>
       </c>
-      <c r="T212" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U212" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -18499,7 +16801,7 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>1297.25</v>
+        <v>1253.38</v>
       </c>
       <c r="Q213" s="2" t="n">
         <v>22966</v>
@@ -18510,14 +16812,6 @@
       <c r="S213" t="n">
         <v>0.035</v>
       </c>
-      <c r="T213" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U213" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -18580,7 +16874,7 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>1709.68</v>
+        <v>1651.86</v>
       </c>
       <c r="Q214" s="2" t="n">
         <v>37703</v>
@@ -18591,14 +16885,6 @@
       <c r="S214" t="n">
         <v>0.035</v>
       </c>
-      <c r="T214" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U214" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -18665,7 +16951,7 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>1302.61</v>
+        <v>1258.56</v>
       </c>
       <c r="Q215" s="2" t="n">
         <v>18780</v>
@@ -18676,14 +16962,6 @@
       <c r="S215" t="n">
         <v>0.035</v>
       </c>
-      <c r="T215" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U215" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -18750,7 +17028,7 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>2156.38</v>
+        <v>2083.46</v>
       </c>
       <c r="Q216" s="2" t="n">
         <v>20297</v>
@@ -18761,14 +17039,6 @@
       <c r="S216" t="n">
         <v>0.035</v>
       </c>
-      <c r="T216" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U216" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -18835,7 +17105,7 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>1791.09</v>
+        <v>1730.52</v>
       </c>
       <c r="Q217" s="2" t="n">
         <v>28727</v>
@@ -18846,14 +17116,6 @@
       <c r="S217" t="n">
         <v>0.035</v>
       </c>
-      <c r="T217" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U217" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -18920,7 +17182,7 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1347.6</v>
+        <v>1302.03</v>
       </c>
       <c r="Q218" s="2" t="n">
         <v>37585</v>
@@ -18931,14 +17193,6 @@
       <c r="S218" t="n">
         <v>0.035</v>
       </c>
-      <c r="T218" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U218" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -19005,7 +17259,7 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>2277.42</v>
+        <v>2200.41</v>
       </c>
       <c r="Q219" s="2" t="n">
         <v>19726</v>
@@ -19016,14 +17270,6 @@
       <c r="S219" t="n">
         <v>0.035</v>
       </c>
-      <c r="T219" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U219" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -19090,7 +17336,7 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>1889.64</v>
+        <v>1825.74</v>
       </c>
       <c r="Q220" s="2" t="n">
         <v>23102</v>
@@ -19101,14 +17347,6 @@
       <c r="S220" t="n">
         <v>0.035</v>
       </c>
-      <c r="T220" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U220" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -19175,7 +17413,7 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>1514.71</v>
+        <v>1463.49</v>
       </c>
       <c r="Q221" s="2" t="n">
         <v>33331</v>
@@ -19186,14 +17424,6 @@
       <c r="S221" t="n">
         <v>0.035</v>
       </c>
-      <c r="T221" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U221" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -19260,7 +17490,7 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>1401.16</v>
+        <v>1353.78</v>
       </c>
       <c r="Q222" s="2" t="n">
         <v>37434</v>
@@ -19271,14 +17501,6 @@
       <c r="S222" t="n">
         <v>0.035</v>
       </c>
-      <c r="T222" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U222" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -19345,7 +17567,7 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>1424.73</v>
+        <v>1376.55</v>
       </c>
       <c r="Q223" s="2" t="n">
         <v>24644</v>
@@ -19356,14 +17578,6 @@
       <c r="S223" t="n">
         <v>0.035</v>
       </c>
-      <c r="T223" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U223" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -19430,7 +17644,7 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>1640.04</v>
+        <v>1584.58</v>
       </c>
       <c r="Q224" s="2" t="n">
         <v>30961</v>
@@ -19441,14 +17655,6 @@
       <c r="S224" t="n">
         <v>0.035</v>
       </c>
-      <c r="T224" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U224" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -19515,7 +17721,7 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>1993.54</v>
+        <v>1926.13</v>
       </c>
       <c r="Q225" s="2" t="n">
         <v>24083</v>
@@ -19526,14 +17732,6 @@
       <c r="S225" t="n">
         <v>0.035</v>
       </c>
-      <c r="T225" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U225" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -19600,7 +17798,7 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>1554.34</v>
+        <v>1501.78</v>
       </c>
       <c r="Q226" s="2" t="n">
         <v>27048</v>
@@ -19611,14 +17809,6 @@
       <c r="S226" t="n">
         <v>0.035</v>
       </c>
-      <c r="T226" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U226" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -19685,7 +17875,7 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>1939.98</v>
+        <v>1874.38</v>
       </c>
       <c r="Q227" s="2" t="n">
         <v>25119</v>
@@ -19696,14 +17886,6 @@
       <c r="S227" t="n">
         <v>0.035</v>
       </c>
-      <c r="T227" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U227" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -19770,23 +17952,15 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>1285.47</v>
+        <v>1242</v>
       </c>
       <c r="Q228" s="2" t="n">
         <v>29642</v>
       </c>
       <c r="R228" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S228" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="T228" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U228" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -19855,7 +18029,7 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>2467.03</v>
+        <v>2383.6</v>
       </c>
       <c r="Q229" s="2" t="n">
         <v>35651</v>
@@ -19866,14 +18040,6 @@
       <c r="S229" t="n">
         <v>0.035</v>
       </c>
-      <c r="T229" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U229" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -19940,7 +18106,7 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>2167.08</v>
+        <v>2093.8</v>
       </c>
       <c r="Q230" s="2" t="n">
         <v>33963</v>
@@ -19951,14 +18117,6 @@
       <c r="S230" t="n">
         <v>0.035</v>
       </c>
-      <c r="T230" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U230" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -20025,7 +18183,7 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>1446.15</v>
+        <v>1397.25</v>
       </c>
       <c r="Q231" s="2" t="n">
         <v>26392</v>
@@ -20036,14 +18194,6 @@
       <c r="S231" t="n">
         <v>0.035</v>
       </c>
-      <c r="T231" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U231" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -20110,7 +18260,7 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>1391.52</v>
+        <v>1344.46</v>
       </c>
       <c r="Q232" s="2" t="n">
         <v>19071</v>
@@ -20121,14 +18271,6 @@
       <c r="S232" t="n">
         <v>0.035</v>
       </c>
-      <c r="T232" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U232" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -20195,7 +18337,7 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>2020.33</v>
+        <v>1952.01</v>
       </c>
       <c r="Q233" s="2" t="n">
         <v>19401</v>
@@ -20206,14 +18348,6 @@
       <c r="S233" t="n">
         <v>0.035</v>
       </c>
-      <c r="T233" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U233" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -20280,7 +18414,7 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>1476.15</v>
+        <v>1426.23</v>
       </c>
       <c r="Q234" s="2" t="n">
         <v>38062</v>
@@ -20291,14 +18425,6 @@
       <c r="S234" t="n">
         <v>0.035</v>
       </c>
-      <c r="T234" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U234" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -20365,7 +18491,7 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>1733.24</v>
+        <v>1674.63</v>
       </c>
       <c r="Q235" s="2" t="n">
         <v>35176</v>
@@ -20376,14 +18502,6 @@
       <c r="S235" t="n">
         <v>0.035</v>
       </c>
-      <c r="T235" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U235" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -20450,7 +18568,7 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>1384.02</v>
+        <v>1337.22</v>
       </c>
       <c r="Q236" s="2" t="n">
         <v>32381</v>
@@ -20461,14 +18579,6 @@
       <c r="S236" t="n">
         <v>0.035</v>
       </c>
-      <c r="T236" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U236" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -20535,7 +18645,7 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>1389.38</v>
+        <v>1342.4</v>
       </c>
       <c r="Q237" s="2" t="n">
         <v>23624</v>
@@ -20546,14 +18656,6 @@
       <c r="S237" t="n">
         <v>0.035</v>
       </c>
-      <c r="T237" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U237" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -20620,7 +18722,7 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>1913.21</v>
+        <v>1848.51</v>
       </c>
       <c r="Q238" s="2" t="n">
         <v>21379</v>
@@ -20631,14 +18733,6 @@
       <c r="S238" t="n">
         <v>0.035</v>
       </c>
-      <c r="T238" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U238" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -20705,7 +18799,7 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>1372.23</v>
+        <v>1325.83</v>
       </c>
       <c r="Q239" s="2" t="n">
         <v>36267</v>
@@ -20716,14 +18810,6 @@
       <c r="S239" t="n">
         <v>0.035</v>
       </c>
-      <c r="T239" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U239" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -20790,7 +18876,7 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>1694.68</v>
+        <v>1637.37</v>
       </c>
       <c r="Q240" s="2" t="n">
         <v>27894</v>
@@ -20801,14 +18887,6 @@
       <c r="S240" t="n">
         <v>0.035</v>
       </c>
-      <c r="T240" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U240" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -20875,7 +18953,7 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>1700.03</v>
+        <v>1642.54</v>
       </c>
       <c r="Q241" s="2" t="n">
         <v>29213</v>
@@ -20886,14 +18964,6 @@
       <c r="S241" t="n">
         <v>0.035</v>
       </c>
-      <c r="T241" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U241" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -20960,7 +19030,7 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>1615.41</v>
+        <v>1560.78</v>
       </c>
       <c r="Q242" s="2" t="n">
         <v>27623</v>
@@ -20971,14 +19041,6 @@
       <c r="S242" t="n">
         <v>0.035</v>
       </c>
-      <c r="T242" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U242" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -21045,7 +19107,7 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>2234.58</v>
+        <v>2159.01</v>
       </c>
       <c r="Q243" s="2" t="n">
         <v>31892</v>
@@ -21056,14 +19118,6 @@
       <c r="S243" t="n">
         <v>0.035</v>
       </c>
-      <c r="T243" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U243" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -21130,7 +19184,7 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>1979.62</v>
+        <v>1912.68</v>
       </c>
       <c r="Q244" s="2" t="n">
         <v>25753</v>
@@ -21141,14 +19195,6 @@
       <c r="S244" t="n">
         <v>0.035</v>
       </c>
-      <c r="T244" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U244" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -21215,7 +19261,7 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>2048.18</v>
+        <v>1978.92</v>
       </c>
       <c r="Q245" s="2" t="n">
         <v>21454</v>
@@ -21226,14 +19272,6 @@
       <c r="S245" t="n">
         <v>0.035</v>
       </c>
-      <c r="T245" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U245" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -21300,7 +19338,7 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>2456.31</v>
+        <v>2373.25</v>
       </c>
       <c r="Q246" s="2" t="n">
         <v>32528</v>
@@ -21311,14 +19349,6 @@
       <c r="S246" t="n">
         <v>0.035</v>
       </c>
-      <c r="T246" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U246" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -21385,7 +19415,7 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>2453.11</v>
+        <v>2370.15</v>
       </c>
       <c r="Q247" s="2" t="n">
         <v>30239</v>
@@ -21396,14 +19426,6 @@
       <c r="S247" t="n">
         <v>0.035</v>
       </c>
-      <c r="T247" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U247" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -21470,7 +19492,7 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>1326.18</v>
+        <v>1281.33</v>
       </c>
       <c r="Q248" s="2" t="n">
         <v>22774</v>
@@ -21481,14 +19503,6 @@
       <c r="S248" t="n">
         <v>0.035</v>
       </c>
-      <c r="T248" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U248" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -21555,7 +19569,7 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>2118.88</v>
+        <v>2047.23</v>
       </c>
       <c r="Q249" s="2" t="n">
         <v>27668</v>
@@ -21566,14 +19580,6 @@
       <c r="S249" t="n">
         <v>0.035</v>
       </c>
-      <c r="T249" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U249" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -21640,7 +19646,7 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>2443.47</v>
+        <v>2360.84</v>
       </c>
       <c r="Q250" s="2" t="n">
         <v>18431</v>
@@ -21651,14 +19657,6 @@
       <c r="S250" t="n">
         <v>0.035</v>
       </c>
-      <c r="T250" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U250" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -21721,7 +19719,7 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>1452.58</v>
+        <v>1403.46</v>
       </c>
       <c r="Q251" s="2" t="n">
         <v>34967</v>
@@ -21732,14 +19730,6 @@
       <c r="S251" t="n">
         <v>0.035</v>
       </c>
-      <c r="T251" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U251" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -21806,7 +19796,7 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>2190.65</v>
+        <v>2116.57</v>
       </c>
       <c r="Q252" s="2" t="n">
         <v>18648</v>
@@ -21817,14 +19807,6 @@
       <c r="S252" t="n">
         <v>0.035</v>
       </c>
-      <c r="T252" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U252" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -21891,7 +19873,7 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>1495.43</v>
+        <v>1444.86</v>
       </c>
       <c r="Q253" s="2" t="n">
         <v>33551</v>
@@ -21902,14 +19884,6 @@
       <c r="S253" t="n">
         <v>0.035</v>
       </c>
-      <c r="T253" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U253" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -21976,7 +19950,7 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>2235.64</v>
+        <v>2160.04</v>
       </c>
       <c r="Q254" s="2" t="n">
         <v>25982</v>
@@ -21987,14 +19961,6 @@
       <c r="S254" t="n">
         <v>0.035</v>
       </c>
-      <c r="T254" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U254" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -22061,7 +20027,7 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>1890.72</v>
+        <v>1826.78</v>
       </c>
       <c r="Q255" s="2" t="n">
         <v>31767</v>
@@ -22072,14 +20038,6 @@
       <c r="S255" t="n">
         <v>0.035</v>
       </c>
-      <c r="T255" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U255" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -22146,7 +20104,7 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>2373.83</v>
+        <v>2293.56</v>
       </c>
       <c r="Q256" s="2" t="n">
         <v>20518</v>
@@ -22157,14 +20115,6 @@
       <c r="S256" t="n">
         <v>0.035</v>
       </c>
-      <c r="T256" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U256" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -22231,7 +20181,7 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>2305.28</v>
+        <v>2227.32</v>
       </c>
       <c r="Q257" s="2" t="n">
         <v>34786</v>
@@ -22242,14 +20192,6 @@
       <c r="S257" t="n">
         <v>0.035</v>
       </c>
-      <c r="T257" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U257" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -22316,7 +20258,7 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>1661.46</v>
+        <v>1605.28</v>
       </c>
       <c r="Q258" s="2" t="n">
         <v>28086</v>
@@ -22327,14 +20269,6 @@
       <c r="S258" t="n">
         <v>0.035</v>
       </c>
-      <c r="T258" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U258" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -22401,7 +20335,7 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>1423.66</v>
+        <v>1375.52</v>
       </c>
       <c r="Q259" s="2" t="n">
         <v>32331</v>
@@ -22412,14 +20346,6 @@
       <c r="S259" t="n">
         <v>0.035</v>
       </c>
-      <c r="T259" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U259" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -22486,7 +20412,7 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>1836.08</v>
+        <v>1773.99</v>
       </c>
       <c r="Q260" s="2" t="n">
         <v>33727</v>
@@ -22497,14 +20423,6 @@
       <c r="S260" t="n">
         <v>0.035</v>
       </c>
-      <c r="T260" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U260" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -22571,7 +20489,7 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>2101.74</v>
+        <v>2030.67</v>
       </c>
       <c r="Q261" s="2" t="n">
         <v>34166</v>
@@ -22582,14 +20500,6 @@
       <c r="S261" t="n">
         <v>0.035</v>
       </c>
-      <c r="T261" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U261" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -22656,7 +20566,7 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>1543.64</v>
+        <v>1491.44</v>
       </c>
       <c r="Q262" s="2" t="n">
         <v>32560</v>
@@ -22667,14 +20577,6 @@
       <c r="S262" t="n">
         <v>0.035</v>
       </c>
-      <c r="T262" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U262" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -22741,7 +20643,7 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>2144.59</v>
+        <v>2072.07</v>
       </c>
       <c r="Q263" s="2" t="n">
         <v>33950</v>
@@ -22752,14 +20654,6 @@
       <c r="S263" t="n">
         <v>0.035</v>
       </c>
-      <c r="T263" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U263" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -22826,7 +20720,7 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>2036.4</v>
+        <v>1967.54</v>
       </c>
       <c r="Q264" s="2" t="n">
         <v>26917</v>
@@ -22837,14 +20731,6 @@
       <c r="S264" t="n">
         <v>0.035</v>
       </c>
-      <c r="T264" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U264" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -22911,7 +20797,7 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>2126.39</v>
+        <v>2054.48</v>
       </c>
       <c r="Q265" s="2" t="n">
         <v>28232</v>
@@ -22922,14 +20808,6 @@
       <c r="S265" t="n">
         <v>0.035</v>
       </c>
-      <c r="T265" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U265" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -22996,7 +20874,7 @@
         </is>
       </c>
       <c r="P266" t="n">
-        <v>1866.07</v>
+        <v>1802.97</v>
       </c>
       <c r="Q266" s="2" t="n">
         <v>34710</v>
@@ -23007,14 +20885,6 @@
       <c r="S266" t="n">
         <v>0.035</v>
       </c>
-      <c r="T266" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U266" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -23081,7 +20951,7 @@
         </is>
       </c>
       <c r="P267" t="n">
-        <v>1869.28</v>
+        <v>1806.07</v>
       </c>
       <c r="Q267" s="2" t="n">
         <v>19633</v>
@@ -23092,14 +20962,6 @@
       <c r="S267" t="n">
         <v>0.035</v>
       </c>
-      <c r="T267" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U267" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -23166,7 +21028,7 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>2079.25</v>
+        <v>2008.94</v>
       </c>
       <c r="Q268" s="2" t="n">
         <v>24813</v>
@@ -23177,14 +21039,6 @@
       <c r="S268" t="n">
         <v>0.035</v>
       </c>
-      <c r="T268" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U268" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -23251,7 +21105,7 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>1735.38</v>
+        <v>1676.7</v>
       </c>
       <c r="Q269" s="2" t="n">
         <v>29942</v>
@@ -23262,14 +21116,6 @@
       <c r="S269" t="n">
         <v>0.035</v>
       </c>
-      <c r="T269" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U269" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -23336,7 +21182,7 @@
         </is>
       </c>
       <c r="P270" t="n">
-        <v>2233.51</v>
+        <v>2157.98</v>
       </c>
       <c r="Q270" s="2" t="n">
         <v>28668</v>
@@ -23347,14 +21193,6 @@
       <c r="S270" t="n">
         <v>0.035</v>
       </c>
-      <c r="T270" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U270" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -23417,7 +21255,7 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>1685.03</v>
+        <v>1628.05</v>
       </c>
       <c r="Q271" s="2" t="n">
         <v>33507</v>
@@ -23428,14 +21266,6 @@
       <c r="S271" t="n">
         <v>0.035</v>
       </c>
-      <c r="T271" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U271" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -23502,7 +21332,7 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>1629.34</v>
+        <v>1574.24</v>
       </c>
       <c r="Q272" s="2" t="n">
         <v>36917</v>
@@ -23513,14 +21343,6 @@
       <c r="S272" t="n">
         <v>0.035</v>
       </c>
-      <c r="T272" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U272" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -23587,7 +21409,7 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>2108.17</v>
+        <v>2036.88</v>
       </c>
       <c r="Q273" s="2" t="n">
         <v>35984</v>
@@ -23598,14 +21420,6 @@
       <c r="S273" t="n">
         <v>0.035</v>
       </c>
-      <c r="T273" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U273" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -23672,7 +21486,7 @@
         </is>
       </c>
       <c r="P274" t="n">
-        <v>1553.28</v>
+        <v>1500.75</v>
       </c>
       <c r="Q274" s="2" t="n">
         <v>31416</v>
@@ -23683,14 +21497,6 @@
       <c r="S274" t="n">
         <v>0.035</v>
       </c>
-      <c r="T274" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U274" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -23757,7 +21563,7 @@
         </is>
       </c>
       <c r="P275" t="n">
-        <v>1543.64</v>
+        <v>1491.44</v>
       </c>
       <c r="Q275" s="2" t="n">
         <v>31357</v>
@@ -23768,14 +21574,6 @@
       <c r="S275" t="n">
         <v>0.035</v>
       </c>
-      <c r="T275" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U275" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -23842,7 +21640,7 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>1454.72</v>
+        <v>1405.53</v>
       </c>
       <c r="Q276" s="2" t="n">
         <v>30361</v>
@@ -23853,14 +21651,6 @@
       <c r="S276" t="n">
         <v>0.035</v>
       </c>
-      <c r="T276" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U276" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -23927,7 +21717,7 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>2350.27</v>
+        <v>2270.79</v>
       </c>
       <c r="Q277" s="2" t="n">
         <v>30145</v>
@@ -23938,14 +21728,6 @@
       <c r="S277" t="n">
         <v>0.035</v>
       </c>
-      <c r="T277" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U277" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -24012,7 +21794,7 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>2144.59</v>
+        <v>2072.07</v>
       </c>
       <c r="Q278" s="2" t="n">
         <v>38380</v>
@@ -24023,14 +21805,6 @@
       <c r="S278" t="n">
         <v>0.035</v>
       </c>
-      <c r="T278" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U278" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -24093,7 +21867,7 @@
         </is>
       </c>
       <c r="P279" t="n">
-        <v>1409.73</v>
+        <v>1362.06</v>
       </c>
       <c r="Q279" s="2" t="n">
         <v>32984</v>
@@ -24104,14 +21878,6 @@
       <c r="S279" t="n">
         <v>0.035</v>
       </c>
-      <c r="T279" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U279" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -24178,7 +21944,7 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>1572.56</v>
+        <v>1519.38</v>
       </c>
       <c r="Q280" s="2" t="n">
         <v>23415</v>
@@ -24189,14 +21955,6 @@
       <c r="S280" t="n">
         <v>0.035</v>
       </c>
-      <c r="T280" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U280" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -24263,7 +22021,7 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>1498.64</v>
+        <v>1447.96</v>
       </c>
       <c r="Q281" s="2" t="n">
         <v>38517</v>
@@ -24274,14 +22032,6 @@
       <c r="S281" t="n">
         <v>0.035</v>
       </c>
-      <c r="T281" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U281" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -24348,7 +22098,7 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>1236.19</v>
+        <v>1194.39</v>
       </c>
       <c r="Q282" s="2" t="n">
         <v>21262</v>
@@ -24359,14 +22109,6 @@
       <c r="S282" t="n">
         <v>0.035</v>
       </c>
-      <c r="T282" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U282" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -24433,7 +22175,7 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>1655.04</v>
+        <v>1599.07</v>
       </c>
       <c r="Q283" s="2" t="n">
         <v>30906</v>
@@ -24444,14 +22186,6 @@
       <c r="S283" t="n">
         <v>0.035</v>
       </c>
-      <c r="T283" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U283" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -24518,7 +22252,7 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>2313.85</v>
+        <v>2235.6</v>
       </c>
       <c r="Q284" s="2" t="n">
         <v>29302</v>
@@ -24529,14 +22263,6 @@
       <c r="S284" t="n">
         <v>0.035</v>
       </c>
-      <c r="T284" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U284" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -24603,7 +22329,7 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>1255.48</v>
+        <v>1213.02</v>
       </c>
       <c r="Q285" s="2" t="n">
         <v>36268</v>
@@ -24614,14 +22340,6 @@
       <c r="S285" t="n">
         <v>0.035</v>
       </c>
-      <c r="T285" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U285" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -24688,7 +22406,7 @@
         </is>
       </c>
       <c r="P286" t="n">
-        <v>2082.46</v>
+        <v>2012.04</v>
       </c>
       <c r="Q286" s="2" t="n">
         <v>34719</v>
@@ -24699,14 +22417,6 @@
       <c r="S286" t="n">
         <v>0.035</v>
       </c>
-      <c r="T286" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U286" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -24773,7 +22483,7 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>1523.28</v>
+        <v>1471.77</v>
       </c>
       <c r="Q287" s="2" t="n">
         <v>25698</v>
@@ -24784,14 +22494,6 @@
       <c r="S287" t="n">
         <v>0.035</v>
       </c>
-      <c r="T287" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U287" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -24858,7 +22560,7 @@
         </is>
       </c>
       <c r="P288" t="n">
-        <v>1912.14</v>
+        <v>1847.48</v>
       </c>
       <c r="Q288" s="2" t="n">
         <v>29872</v>
@@ -24869,14 +22571,6 @@
       <c r="S288" t="n">
         <v>0.035</v>
       </c>
-      <c r="T288" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U288" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -24943,7 +22637,7 @@
         </is>
       </c>
       <c r="P289" t="n">
-        <v>2278.49</v>
+        <v>2201.44</v>
       </c>
       <c r="Q289" s="2" t="n">
         <v>26057</v>
@@ -24954,14 +22648,6 @@
       <c r="S289" t="n">
         <v>0.035</v>
       </c>
-      <c r="T289" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U289" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -25028,7 +22714,7 @@
         </is>
       </c>
       <c r="P290" t="n">
-        <v>1726.81</v>
+        <v>1668.42</v>
       </c>
       <c r="Q290" s="2" t="n">
         <v>20257</v>
@@ -25039,14 +22725,6 @@
       <c r="S290" t="n">
         <v>0.035</v>
       </c>
-      <c r="T290" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U290" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -25113,7 +22791,7 @@
         </is>
       </c>
       <c r="P291" t="n">
-        <v>1796.45</v>
+        <v>1735.7</v>
       </c>
       <c r="Q291" s="2" t="n">
         <v>20150</v>
@@ -25124,14 +22802,6 @@
       <c r="S291" t="n">
         <v>0.035</v>
       </c>
-      <c r="T291" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U291" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -25198,7 +22868,7 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>1286.54</v>
+        <v>1243.03</v>
       </c>
       <c r="Q292" s="2" t="n">
         <v>33197</v>
@@ -25209,14 +22879,6 @@
       <c r="S292" t="n">
         <v>0.035</v>
       </c>
-      <c r="T292" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U292" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -25283,7 +22945,7 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>1730.02</v>
+        <v>1671.52</v>
       </c>
       <c r="Q293" s="2" t="n">
         <v>23937</v>
@@ -25294,14 +22956,6 @@
       <c r="S293" t="n">
         <v>0.035</v>
       </c>
-      <c r="T293" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U293" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -25368,7 +23022,7 @@
         </is>
       </c>
       <c r="P294" t="n">
-        <v>1680.76</v>
+        <v>1623.92</v>
       </c>
       <c r="Q294" s="2" t="n">
         <v>32923</v>
@@ -25379,14 +23033,6 @@
       <c r="S294" t="n">
         <v>0.035</v>
       </c>
-      <c r="T294" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U294" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -25453,7 +23099,7 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>1306.89</v>
+        <v>1262.7</v>
       </c>
       <c r="Q295" s="2" t="n">
         <v>32228</v>
@@ -25464,14 +23110,6 @@
       <c r="S295" t="n">
         <v>0.035</v>
       </c>
-      <c r="T295" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U295" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -25538,7 +23176,7 @@
         </is>
       </c>
       <c r="P296" t="n">
-        <v>2197.08</v>
+        <v>2122.78</v>
       </c>
       <c r="Q296" s="2" t="n">
         <v>23961</v>
@@ -25549,14 +23187,6 @@
       <c r="S296" t="n">
         <v>0.035</v>
       </c>
-      <c r="T296" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U296" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -25619,7 +23249,7 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>1695.74</v>
+        <v>1638.4</v>
       </c>
       <c r="Q297" s="2" t="n">
         <v>31098</v>
@@ -25630,14 +23260,6 @@
       <c r="S297" t="n">
         <v>0.035</v>
       </c>
-      <c r="T297" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U297" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -25704,23 +23326,15 @@
         </is>
       </c>
       <c r="P298" t="n">
-        <v>2441.32</v>
+        <v>2358.76</v>
       </c>
       <c r="Q298" s="2" t="n">
         <v>33660</v>
       </c>
       <c r="R298" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S298" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="T298" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U298" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -25789,7 +23403,7 @@
         </is>
       </c>
       <c r="P299" t="n">
-        <v>1984.97</v>
+        <v>1917.85</v>
       </c>
       <c r="Q299" s="2" t="n">
         <v>23842</v>
@@ -25800,14 +23414,6 @@
       <c r="S299" t="n">
         <v>0.035</v>
       </c>
-      <c r="T299" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U299" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -25874,7 +23480,7 @@
         </is>
       </c>
       <c r="P300" t="n">
-        <v>1857.5</v>
+        <v>1794.69</v>
       </c>
       <c r="Q300" s="2" t="n">
         <v>28411</v>
@@ -25885,14 +23491,6 @@
       <c r="S300" t="n">
         <v>0.035</v>
       </c>
-      <c r="T300" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U300" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -25959,7 +23557,7 @@
         </is>
       </c>
       <c r="P301" t="n">
-        <v>1569.35</v>
+        <v>1516.28</v>
       </c>
       <c r="Q301" s="2" t="n">
         <v>21630</v>
@@ -25970,14 +23568,6 @@
       <c r="S301" t="n">
         <v>0.035</v>
       </c>
-      <c r="T301" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U301" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -26044,23 +23634,15 @@
         </is>
       </c>
       <c r="P302" t="n">
-        <v>1225.48</v>
+        <v>1184.04</v>
       </c>
       <c r="Q302" s="2" t="n">
         <v>19415</v>
       </c>
       <c r="R302" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S302" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="T302" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U302" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -26129,7 +23711,7 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>1658.26</v>
+        <v>1602.18</v>
       </c>
       <c r="Q303" s="2" t="n">
         <v>31295</v>
@@ -26140,14 +23722,6 @@
       <c r="S303" t="n">
         <v>0.035</v>
       </c>
-      <c r="T303" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U303" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -26214,7 +23788,7 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>2148.88</v>
+        <v>2076.21</v>
       </c>
       <c r="Q304" s="2" t="n">
         <v>35887</v>
@@ -26225,14 +23799,6 @@
       <c r="S304" t="n">
         <v>0.035</v>
       </c>
-      <c r="T304" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U304" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -26295,7 +23861,7 @@
         </is>
       </c>
       <c r="P305" t="n">
-        <v>1552.21</v>
+        <v>1499.72</v>
       </c>
       <c r="Q305" s="2" t="n">
         <v>28350</v>
@@ -26306,14 +23872,6 @@
       <c r="S305" t="n">
         <v>0.035</v>
       </c>
-      <c r="T305" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U305" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -26380,7 +23938,7 @@
         </is>
       </c>
       <c r="P306" t="n">
-        <v>1787.88</v>
+        <v>1727.42</v>
       </c>
       <c r="Q306" s="2" t="n">
         <v>33841</v>
@@ -26391,14 +23949,6 @@
       <c r="S306" t="n">
         <v>0.035</v>
       </c>
-      <c r="T306" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U306" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -26465,7 +24015,7 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>1357.24</v>
+        <v>1311.34</v>
       </c>
       <c r="Q307" s="2" t="n">
         <v>21311</v>
@@ -26476,14 +24026,6 @@
       <c r="S307" t="n">
         <v>0.035</v>
       </c>
-      <c r="T307" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U307" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -26550,7 +24092,7 @@
         </is>
       </c>
       <c r="P308" t="n">
-        <v>1513.65</v>
+        <v>1462.46</v>
       </c>
       <c r="Q308" s="2" t="n">
         <v>19180</v>
@@ -26561,14 +24103,6 @@
       <c r="S308" t="n">
         <v>0.035</v>
       </c>
-      <c r="T308" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U308" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -26635,7 +24169,7 @@
         </is>
       </c>
       <c r="P309" t="n">
-        <v>1791.09</v>
+        <v>1730.52</v>
       </c>
       <c r="Q309" s="2" t="n">
         <v>29391</v>
@@ -26646,14 +24180,6 @@
       <c r="S309" t="n">
         <v>0.035</v>
       </c>
-      <c r="T309" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U309" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -26720,7 +24246,7 @@
         </is>
       </c>
       <c r="P310" t="n">
-        <v>1686.11</v>
+        <v>1629.09</v>
       </c>
       <c r="Q310" s="2" t="n">
         <v>18394</v>
@@ -26731,14 +24257,6 @@
       <c r="S310" t="n">
         <v>0.035</v>
       </c>
-      <c r="T310" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U310" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -26805,7 +24323,7 @@
         </is>
       </c>
       <c r="P311" t="n">
-        <v>2031.04</v>
+        <v>1962.36</v>
       </c>
       <c r="Q311" s="2" t="n">
         <v>35128</v>
@@ -26816,14 +24334,6 @@
       <c r="S311" t="n">
         <v>0.035</v>
       </c>
-      <c r="T311" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U311" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -26890,7 +24400,7 @@
         </is>
       </c>
       <c r="P312" t="n">
-        <v>2125.31</v>
+        <v>2053.44</v>
       </c>
       <c r="Q312" s="2" t="n">
         <v>25864</v>
@@ -26901,14 +24411,6 @@
       <c r="S312" t="n">
         <v>0.035</v>
       </c>
-      <c r="T312" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U312" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -26975,7 +24477,7 @@
         </is>
       </c>
       <c r="P313" t="n">
-        <v>1364.74</v>
+        <v>1318.59</v>
       </c>
       <c r="Q313" s="2" t="n">
         <v>25522</v>
@@ -26986,14 +24488,6 @@
       <c r="S313" t="n">
         <v>0.035</v>
       </c>
-      <c r="T313" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U313" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -27056,7 +24550,7 @@
         </is>
       </c>
       <c r="P314" t="n">
-        <v>2249.57</v>
+        <v>2173.5</v>
       </c>
       <c r="Q314" s="2" t="n">
         <v>36673</v>
@@ -27067,14 +24561,6 @@
       <c r="S314" t="n">
         <v>0.035</v>
       </c>
-      <c r="T314" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U314" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -27141,7 +24627,7 @@
         </is>
       </c>
       <c r="P315" t="n">
-        <v>1760.02</v>
+        <v>1700.5</v>
       </c>
       <c r="Q315" s="2" t="n">
         <v>19329</v>
@@ -27152,14 +24638,6 @@
       <c r="S315" t="n">
         <v>0.035</v>
       </c>
-      <c r="T315" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U315" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -27226,7 +24704,7 @@
         </is>
       </c>
       <c r="P316" t="n">
-        <v>1781.44</v>
+        <v>1721.2</v>
       </c>
       <c r="Q316" s="2" t="n">
         <v>38712</v>
@@ -27237,14 +24715,6 @@
       <c r="S316" t="n">
         <v>0.035</v>
       </c>
-      <c r="T316" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U316" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -27311,7 +24781,7 @@
         </is>
       </c>
       <c r="P317" t="n">
-        <v>1512.57</v>
+        <v>1461.42</v>
       </c>
       <c r="Q317" s="2" t="n">
         <v>31224</v>
@@ -27322,14 +24792,6 @@
       <c r="S317" t="n">
         <v>0.035</v>
       </c>
-      <c r="T317" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U317" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -27396,7 +24858,7 @@
         </is>
       </c>
       <c r="P318" t="n">
-        <v>1343.32</v>
+        <v>1297.89</v>
       </c>
       <c r="Q318" s="2" t="n">
         <v>20828</v>
@@ -27407,14 +24869,6 @@
       <c r="S318" t="n">
         <v>0.035</v>
       </c>
-      <c r="T318" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U318" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -27481,7 +24935,7 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>2177.8</v>
+        <v>2104.15</v>
       </c>
       <c r="Q319" s="2" t="n">
         <v>21272</v>
@@ -27490,14 +24944,6 @@
         <v>67</v>
       </c>
       <c r="S319" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="T319" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="U319" t="n">
         <v>0.035</v>
       </c>
     </row>
